--- a/LISTAS DE BUENA FE AFA SOMOS TODOS 2026/CLAYPOLE 2.xlsx
+++ b/LISTAS DE BUENA FE AFA SOMOS TODOS 2026/CLAYPOLE 2.xlsx
@@ -299,759 +299,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>891540</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>914400</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="1 Imagen" descr="veronica anahi avila.jfif">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="8930640" y="3939540"/>
-          <a:ext cx="891540" cy="914400"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>883920</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="2 Imagen" descr="magali fernandez.jfif">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="8930640" y="4861560"/>
-          <a:ext cx="883920" cy="914400"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>944880</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>952500</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="3 Imagen" descr="yasmin romero.jfif">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000004000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="8930640" y="6720840"/>
-          <a:ext cx="944880" cy="952500"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>967740</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>922020</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="4 Imagen" descr="lucia machado.jfif">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000005000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="8930640" y="8641080"/>
-          <a:ext cx="967740" cy="922020"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>990600</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>1082040</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="5 Imagen" descr="nahir dietz.jfif">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000006000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="8930640" y="10538460"/>
-          <a:ext cx="990600" cy="1082040"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>22860</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>1028700</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>15240</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="7" name="6 Imagen" descr="aldana andreoli.jfif">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000007000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="8938260" y="11681460"/>
-          <a:ext cx="1021080" cy="1036320"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>22860</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>1059180</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>1424940</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="8" name="7 Imagen" descr="bruno bonifas yanet.jfif">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000008000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="8938260" y="13845540"/>
-          <a:ext cx="1051560" cy="1402080"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>1028700</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>1074420</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="9" name="8 Imagen" descr="juliana aboy.jfif">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000009000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="8930640" y="15262860"/>
-          <a:ext cx="1028700" cy="1074420"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>1013460</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>1074420</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="10" name="9 Imagen" descr="micaela zocco.jfif">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000A000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="8930640" y="16352520"/>
-          <a:ext cx="1013460" cy="1074420"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>1264920</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>982980</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="11" name="10 Imagen" descr="PROFE SERGIO.jfif">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000B000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="8930640" y="19697700"/>
-          <a:ext cx="1264920" cy="982980"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>1097280</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>15240</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>1295400</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="12" name="11 Imagen" descr="PROFE WALTER.jfif">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000C000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="8923020" y="20627340"/>
-          <a:ext cx="1303020" cy="1104900"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>922020</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>7620</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="13" name="12 Imagen" descr="VALERIA BASUALDO.jfif">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000D000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="8930640" y="5775960"/>
-          <a:ext cx="922020" cy="952500"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>975360</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>944880</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="14" name="13 Imagen" descr="CELESTE MACHADO.jfif">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000E000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="8930640" y="7688580"/>
-          <a:ext cx="975360" cy="944880"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>982980</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>15240</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="15" name="14 Imagen" descr="NICOLE NARANJO.jfif">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000F000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId14" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="8930640" y="9578340"/>
-          <a:ext cx="982980" cy="975360"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>1043940</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="16" name="15 Imagen" descr="LUANA ROLDAN.jfif">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000010000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId15" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="8930640" y="12702540"/>
-          <a:ext cx="1043940" cy="1120140"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>1082040</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>7620</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="17" name="16 Imagen" descr="LUJAN SOSA.jfif">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000011000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId16" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="8930640" y="17434560"/>
-          <a:ext cx="1082040" cy="960120"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>876300</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>22860</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="18" name="17 Imagen" descr="EVELIN SEGOVIA.jfif">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000012000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId17" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="8930640" y="2994660"/>
-          <a:ext cx="876300" cy="967740"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
